--- a/feedback_forms/050_online_retail_platform_usability_evaluation_form--feedback_forms.xlsx
+++ b/feedback_forms/050_online_retail_platform_usability_evaluation_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>platform_experience</t>
+          <t>platform_experience_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>rating_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>Rating 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -984,12 +984,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>company_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Company 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>job_title_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Job Title 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Name 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
